--- a/ig/document/StructureDefinition-medcom-document-homecommunityid-extension.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-homecommunityid-extension.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1499,7 +1499,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>109</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>120</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>135</v>
       </c>
@@ -2343,12 +2343,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK14">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-homecommunityid-extension.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-homecommunityid-extension.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
